--- a/static_apf/results/static_apf_5_environments.xlsx
+++ b/static_apf/results/static_apf_5_environments.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Static_APF_5_Envs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Static_APF_5_Envs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111.3</v>
+        <v>290.1</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15.2 W</t>
+          <t>2.6 W</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>750.6</v>
+        <v>741.6</v>
       </c>
     </row>
     <row r="14">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63.9</v>
+        <v>209.9</v>
       </c>
     </row>
     <row r="23">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="24">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +660,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18.9 W</t>
+          <t>2.3 W</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>716.7</v>
+        <v>707.4</v>
       </c>
     </row>
     <row r="27">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84.8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="35">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68.40000000000001</v>
+        <v>357.5</v>
       </c>
     </row>
     <row r="36">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="37">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="38">
@@ -773,7 +773,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21.9 W</t>
+          <t>4.1 W</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>705.61</v>
+        <v>696.6</v>
       </c>
     </row>
     <row r="40">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>86.2</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="43">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="48">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>138.4</v>
+        <v>399</v>
       </c>
     </row>
     <row r="49">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="50">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="51">
@@ -886,7 +886,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23.8 W</t>
+          <t>2.4 W</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>789.71</v>
+        <v>781.2</v>
       </c>
     </row>
     <row r="53">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>77</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="56">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1544.9</v>
+        <v>4853.4</v>
       </c>
     </row>
     <row r="62">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>18.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="63">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="64">
@@ -999,7 +999,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>33.1 W</t>
+          <t>1.8 W</t>
         </is>
       </c>
     </row>
@@ -1105,27 +1105,27 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>111.3</v>
+        <v>290.1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>23.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>15.2 W</t>
+          <t>2.6 W</t>
         </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>750.6</v>
+        <v>741.6</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
@@ -1146,27 +1146,27 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>63.9</v>
+        <v>209.9</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>19.7</v>
+        <v>12.4</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>18.9 W</t>
+          <t>2.3 W</t>
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>716.7</v>
+        <v>707.4</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>84.8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75">
@@ -1187,27 +1187,27 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>68.40000000000001</v>
+        <v>357.5</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>19.8</v>
+        <v>11.8</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>21.9 W</t>
+          <t>4.1 W</t>
         </is>
       </c>
       <c r="J75" s="5" t="n">
-        <v>705.61</v>
+        <v>696.6</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>86.2</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="76">
@@ -1228,27 +1228,27 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>138.4</v>
+        <v>399</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>27.4</v>
+        <v>6.2</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.66</v>
+        <v>0.08</v>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>23.8 W</t>
+          <t>2.4 W</t>
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>789.71</v>
+        <v>781.2</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>77</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="77">
@@ -1272,17 +1272,17 @@
         <v>6000</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>1544.9</v>
+        <v>4853.4</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>18.4</v>
+        <v>1.2</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>33.1 W</t>
+          <t>1.8 W</t>
         </is>
       </c>
       <c r="J77" s="5" t="n">
